--- a/Collections/Foreign_various/Foreighn_originals.xlsx
+++ b/Collections/Foreign_various/Foreighn_originals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Foreign_various\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A25818-2D14-4044-92D8-3EB559E53A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFDC176-98C5-4060-B519-A1025FB724F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Europe" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="266">
   <si>
     <t>-</t>
   </si>
@@ -857,6 +857,18 @@
   </si>
   <si>
     <t>Beijing Opera</t>
+  </si>
+  <si>
+    <t>Belarus</t>
+  </si>
+  <si>
+    <t>1 kopek</t>
+  </si>
+  <si>
+    <t>2 kopeks</t>
+  </si>
+  <si>
+    <t>Thick rays, convex star /Arms type 1995/</t>
   </si>
 </sst>
 </file>
@@ -2232,7 +2244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -3590,63 +3602,67 @@
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
-        <v>2000</v>
+        <v>2009</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>58</v>
+        <v>262</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D55" s="4"/>
+        <v>263</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>265</v>
+      </c>
       <c r="E55" s="4"/>
       <c r="F55" s="5">
         <v>1</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H55" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I55" s="4">
-        <v>0.11</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
-        <v>1974</v>
+        <v>2009</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>58</v>
+        <v>262</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D56" s="4"/>
+        <v>264</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>265</v>
+      </c>
       <c r="E56" s="4"/>
       <c r="F56" s="5">
         <v>1</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H56" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I56" s="4">
-        <v>0.1</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -3654,24 +3670,24 @@
         <v>1</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H57" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I57" s="4">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
-        <v>1999</v>
+        <v>1974</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -3679,13 +3695,13 @@
         <v>1</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H58" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I58" s="4">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3696,7 +3712,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -3710,7 +3726,7 @@
         <v>10</v>
       </c>
       <c r="I59" s="4">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3721,7 +3737,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -3729,24 +3745,24 @@
         <v>1</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H60" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I60" s="4">
-        <v>0.28000000000000003</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
-        <v>1995</v>
+        <v>1999</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -3760,18 +3776,18 @@
         <v>10</v>
       </c>
       <c r="I61" s="4">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
-        <v>2003</v>
+        <v>1999</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -3785,18 +3801,18 @@
         <v>10</v>
       </c>
       <c r="I62" s="4">
-        <v>0.42</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
-        <v>2001</v>
+        <v>1995</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -3810,18 +3826,18 @@
         <v>10</v>
       </c>
       <c r="I63" s="4">
-        <v>1.48</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -3835,18 +3851,18 @@
         <v>10</v>
       </c>
       <c r="I64" s="4">
-        <v>0.17</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -3854,24 +3870,24 @@
         <v>1</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H65" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I65" s="4">
-        <v>0.28999999999999998</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -3879,24 +3895,24 @@
         <v>1</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H66" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I66" s="4">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
@@ -3910,18 +3926,18 @@
         <v>10</v>
       </c>
       <c r="I67" s="4">
-        <v>0.13</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -3935,7 +3951,7 @@
         <v>10</v>
       </c>
       <c r="I68" s="4">
-        <v>0.14000000000000001</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3946,7 +3962,7 @@
         <v>70</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -3960,18 +3976,18 @@
         <v>10</v>
       </c>
       <c r="I69" s="4">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -3979,24 +3995,24 @@
         <v>1</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H70" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I70" s="4">
-        <v>0.19</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -4010,7 +4026,7 @@
         <v>10</v>
       </c>
       <c r="I71" s="4">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4021,7 +4037,7 @@
         <v>70</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -4029,24 +4045,24 @@
         <v>1</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H72" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I72" s="4">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
-        <v>1986</v>
+        <v>2005</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
@@ -4060,18 +4076,18 @@
         <v>10</v>
       </c>
       <c r="I73" s="4">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -4079,24 +4095,24 @@
         <v>1</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H74" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I74" s="4">
-        <v>0.28000000000000003</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
-        <v>1991</v>
+        <v>1986</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
@@ -4104,24 +4120,24 @@
         <v>1</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H75" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I75" s="4">
-        <v>0.38</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
-        <v>1991</v>
+        <v>2004</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -4129,24 +4145,24 @@
         <v>1</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H76" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I76" s="4">
-        <v>0.09</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
-        <v>1997</v>
+        <v>1991</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -4154,24 +4170,24 @@
         <v>1</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="H77" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I77" s="4">
-        <v>0.14000000000000001</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
-        <v>2013</v>
+        <v>1991</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
@@ -4185,18 +4201,18 @@
         <v>10</v>
       </c>
       <c r="I78" s="4">
-        <v>0.59</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
@@ -4204,24 +4220,24 @@
         <v>1</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="H79" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I79" s="4">
-        <v>0.25</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -4229,24 +4245,24 @@
         <v>1</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H80" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I80" s="4">
-        <v>0.33</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
-        <v>2009</v>
+        <v>1998</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -4254,24 +4270,24 @@
         <v>1</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H81" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I81" s="4">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
-        <v>1998</v>
+        <v>2007</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
@@ -4285,18 +4301,18 @@
         <v>10</v>
       </c>
       <c r="I82" s="4">
-        <v>0.88</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -4304,24 +4320,24 @@
         <v>1</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H83" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I83" s="4">
-        <v>0.85</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
-        <v>1978</v>
-      </c>
-      <c r="B84" s="15" t="s">
-        <v>103</v>
+        <v>1998</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -4335,18 +4351,18 @@
         <v>10</v>
       </c>
       <c r="I84" s="4">
-        <v>0.22</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
-        <v>1978</v>
-      </c>
-      <c r="B85" s="15" t="s">
-        <v>103</v>
+        <v>2008</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
@@ -4354,24 +4370,24 @@
         <v>1</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H85" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I85" s="4">
-        <v>0.12</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
-        <v>1967</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>68</v>
+        <v>1978</v>
+      </c>
+      <c r="B86" s="15" t="s">
+        <v>103</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -4379,24 +4395,24 @@
         <v>1</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H86" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I86" s="4">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
-        <v>1987</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>68</v>
+        <v>1978</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>103</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
@@ -4404,24 +4420,24 @@
         <v>1</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="H87" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I87" s="4">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
-        <v>1980</v>
+        <v>1967</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
@@ -4429,7 +4445,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H88" s="13" t="s">
         <v>10</v>
@@ -4440,13 +4456,13 @@
     </row>
     <row r="89" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -4454,24 +4470,24 @@
         <v>1</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="H89" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I89" s="4">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
-        <v>1989</v>
+        <v>1980</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -4479,24 +4495,24 @@
         <v>1</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H90" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I90" s="4">
-        <v>0.28000000000000003</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
-        <v>1980</v>
+        <v>1985</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
@@ -4510,18 +4526,18 @@
         <v>10</v>
       </c>
       <c r="I91" s="4">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
-        <v>1993</v>
+        <v>1989</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -4535,18 +4551,18 @@
         <v>10</v>
       </c>
       <c r="I92" s="4">
-        <v>0.11</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
-        <v>1993</v>
+        <v>1980</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
@@ -4560,7 +4576,7 @@
         <v>10</v>
       </c>
       <c r="I93" s="4">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4571,7 +4587,7 @@
         <v>109</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
@@ -4579,13 +4595,13 @@
         <v>1</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H94" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I94" s="4">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4596,7 +4612,7 @@
         <v>109</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -4610,18 +4626,18 @@
         <v>10</v>
       </c>
       <c r="I95" s="4">
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
@@ -4635,7 +4651,7 @@
         <v>10</v>
       </c>
       <c r="I96" s="4">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4646,7 +4662,7 @@
         <v>109</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -4654,24 +4670,24 @@
         <v>1</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H97" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I97" s="4">
-        <v>0.25</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
@@ -4679,24 +4695,24 @@
         <v>1</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H98" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I98" s="4">
-        <v>0.44</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
@@ -4704,24 +4720,24 @@
         <v>1</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H99" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I99" s="4">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -4735,18 +4751,18 @@
         <v>10</v>
       </c>
       <c r="I100" s="4">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
-        <v>1996</v>
+        <v>1992</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>123</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -4754,24 +4770,24 @@
         <v>1</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H101" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I101" s="4">
-        <v>3.11</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
-        <v>2004</v>
+        <v>1990</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -4785,18 +4801,18 @@
         <v>10</v>
       </c>
       <c r="I102" s="4">
-        <v>0.24</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
-        <v>2000</v>
+        <v>1996</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -4804,24 +4820,24 @@
         <v>1</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H103" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I103" s="4">
-        <v>0.34</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
@@ -4829,24 +4845,24 @@
         <v>1</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="H104" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I104" s="4">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
-        <v>2014</v>
+        <v>2000</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
@@ -4854,24 +4870,24 @@
         <v>1</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="H105" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I105" s="4">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
@@ -4879,24 +4895,24 @@
         <v>1</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="H106" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I106" s="4">
-        <v>0.53</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
-        <v>2003</v>
+        <v>2014</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
@@ -4904,12 +4920,62 @@
         <v>1</v>
       </c>
       <c r="G107" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H107" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I107" s="4">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="5">
+        <v>1</v>
+      </c>
+      <c r="G108" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H107" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="I107" s="4">
+      <c r="H108" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I108" s="4">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="5">
+        <v>1</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H109" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I109" s="4">
         <v>0.59</v>
       </c>
     </row>
@@ -4921,12 +4987,12 @@
     <mergeCell ref="C1:G1"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="F3 F73:F75 F5 F11:F12 F14:F21 F86 F63:F70 F23:F30 F50:F61 F32:F45 F7:F9">
+  <conditionalFormatting sqref="F3 F75:F77 F5 F11:F12 F14:F21 F88 F65:F72 F23:F30 F32:F45 F7:F9 F50:F63">
     <cfRule type="containsText" dxfId="91" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F73:F75 F3 F5 F11:F12 F14:F21 F63:F70 F86 F23:F30 F50:F61 F32:F45 F7:F9">
+  <conditionalFormatting sqref="F75:F77 F3 F5 F11:F12 F14:F21 F65:F72 F88 F23:F30 F32:F45 F7:F9 F50:F63">
     <cfRule type="colorScale" priority="86">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4955,12 +5021,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F76:F81 F83:F90">
+  <conditionalFormatting sqref="F78:F83 F85:F92">
     <cfRule type="containsText" dxfId="89" priority="59" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F76))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F76:F81 F83:F90">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F78))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F78:F83 F85:F92">
     <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4972,12 +5038,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F62">
+  <conditionalFormatting sqref="F64">
     <cfRule type="containsText" dxfId="88" priority="57" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F62))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F62">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F64))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F64">
     <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4989,12 +5055,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F71">
+  <conditionalFormatting sqref="F73">
     <cfRule type="containsText" dxfId="87" priority="55" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F71))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F71">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F73))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F73">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5006,12 +5072,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F72">
+  <conditionalFormatting sqref="F74">
     <cfRule type="containsText" dxfId="86" priority="53" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F72))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F72">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F74))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F74">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5057,12 +5123,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F82">
+  <conditionalFormatting sqref="F84">
     <cfRule type="containsText" dxfId="83" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F82))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F82">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F84))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F84">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5074,12 +5140,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F99">
+  <conditionalFormatting sqref="F101">
     <cfRule type="containsText" dxfId="82" priority="45" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F99))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F99">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F101))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F101">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5091,12 +5157,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F100:F104">
+  <conditionalFormatting sqref="F102:F106">
     <cfRule type="containsText" dxfId="81" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F100))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F100:F104">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F102))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F102:F106">
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5108,12 +5174,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F91">
+  <conditionalFormatting sqref="F93">
     <cfRule type="containsText" dxfId="80" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F91))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F91">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F93))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F93">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5125,12 +5191,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F92">
+  <conditionalFormatting sqref="F94">
     <cfRule type="containsText" dxfId="79" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F92))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F92">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F94))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F94">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5142,12 +5208,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F93">
+  <conditionalFormatting sqref="F95">
     <cfRule type="containsText" dxfId="78" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F93))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F93">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F95))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F95">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5159,12 +5225,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F94">
+  <conditionalFormatting sqref="F96">
     <cfRule type="containsText" dxfId="77" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F94))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F94">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F96))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F96">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5176,12 +5242,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F95">
+  <conditionalFormatting sqref="F97">
     <cfRule type="containsText" dxfId="76" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F95))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F95">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F97))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F97">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5193,12 +5259,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F96">
+  <conditionalFormatting sqref="F98">
     <cfRule type="containsText" dxfId="75" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F96))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F96">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F98))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F98">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5210,12 +5276,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F97">
+  <conditionalFormatting sqref="F99">
     <cfRule type="containsText" dxfId="74" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F97))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F97">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F99))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F99">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5227,12 +5293,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F98">
+  <conditionalFormatting sqref="F100">
     <cfRule type="containsText" dxfId="73" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F98))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F98">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F100))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F100">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5346,12 +5412,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F105">
+  <conditionalFormatting sqref="F107">
     <cfRule type="containsText" dxfId="66" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F105))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F105">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F107))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F107">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5363,12 +5429,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F106">
+  <conditionalFormatting sqref="F108">
     <cfRule type="containsText" dxfId="65" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F106))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F106">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F108))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F108">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5380,12 +5446,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F107">
+  <conditionalFormatting sqref="F109">
     <cfRule type="containsText" dxfId="64" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F107))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F107">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F109))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F109">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5423,44 +5489,44 @@
     <hyperlink ref="H51" r:id="rId23" xr:uid="{5A09ADB0-F08A-4609-87DE-786FCA31E493}"/>
     <hyperlink ref="H52" r:id="rId24" xr:uid="{571B95A7-4FFC-4966-9B5C-FD99C13F51EA}"/>
     <hyperlink ref="H54" r:id="rId25" xr:uid="{FCB9ADB7-2CA7-4FCE-8E7E-DEC9CF2BA222}"/>
-    <hyperlink ref="H56" r:id="rId26" xr:uid="{8A7988FE-9A8C-4412-9EA2-FA9C2448DD52}"/>
-    <hyperlink ref="H57" r:id="rId27" xr:uid="{140048C0-36FA-4F5F-8C86-5359A352CAAA}"/>
+    <hyperlink ref="H58" r:id="rId26" xr:uid="{8A7988FE-9A8C-4412-9EA2-FA9C2448DD52}"/>
+    <hyperlink ref="H59" r:id="rId27" xr:uid="{140048C0-36FA-4F5F-8C86-5359A352CAAA}"/>
     <hyperlink ref="H11" r:id="rId28" xr:uid="{54B623BC-DB92-4E8C-881B-D09C461517F4}"/>
     <hyperlink ref="H9" r:id="rId29" xr:uid="{1336EED8-0577-4106-A205-CEBD23169959}"/>
-    <hyperlink ref="H58" r:id="rId30" xr:uid="{5AE8628B-A6AC-4465-BD4E-F82D7A992971}"/>
-    <hyperlink ref="H61" r:id="rId31" xr:uid="{5CF7566F-CBE0-4F25-9013-93E6C3867D34}"/>
-    <hyperlink ref="H86" r:id="rId32" xr:uid="{1C353C88-9EE8-4F55-ABF4-3CDB7B4E6AFA}"/>
-    <hyperlink ref="H68" r:id="rId33" xr:uid="{A4884050-FCBA-4619-993B-8E09E8C3C70B}"/>
-    <hyperlink ref="H70" r:id="rId34" xr:uid="{58D76656-D3D8-42D0-BC20-8510076538AB}"/>
-    <hyperlink ref="H73" r:id="rId35" xr:uid="{C0E7B505-5AEC-4726-BC3C-849B7BDA23D9}"/>
-    <hyperlink ref="H59" r:id="rId36" xr:uid="{8C7DE950-390F-4072-944E-544CAC30E1E2}"/>
-    <hyperlink ref="H62" r:id="rId37" xr:uid="{B704CBA7-EC39-4C16-9B7C-5A1F23168BB8}"/>
-    <hyperlink ref="H66" r:id="rId38" xr:uid="{77992806-B822-4851-8E7E-B16BCD52945D}"/>
-    <hyperlink ref="H69" r:id="rId39" xr:uid="{70DB7A6C-EE09-443B-AD3C-19A4D772B8A8}"/>
-    <hyperlink ref="H64" r:id="rId40" xr:uid="{D424DDC5-5012-4B92-A954-F4FB9A628B30}"/>
-    <hyperlink ref="H74" r:id="rId41" xr:uid="{0B10C842-555F-4DE2-9434-D8A68A89D8EB}"/>
-    <hyperlink ref="H60" r:id="rId42" xr:uid="{C77D7737-0D5E-4663-A3E3-874018F1FFE3}"/>
-    <hyperlink ref="H63" r:id="rId43" xr:uid="{F1705702-B968-4193-861D-2AB08339CEE2}"/>
-    <hyperlink ref="H67" r:id="rId44" xr:uid="{D1806A47-31AD-4D52-9D39-FCC2CFADBCA7}"/>
-    <hyperlink ref="H72" r:id="rId45" xr:uid="{6D5ED102-4BF2-4DF0-9937-E6866027A220}"/>
-    <hyperlink ref="H75" r:id="rId46" xr:uid="{772C27DA-BD2C-4F9A-A4D3-5C6979B2A4F9}"/>
-    <hyperlink ref="H77" r:id="rId47" xr:uid="{EE876AD6-690E-4842-9C9C-46D511C113AC}"/>
-    <hyperlink ref="H80" r:id="rId48" xr:uid="{EDBE8CFB-1752-473F-8585-E99FE96B416C}"/>
-    <hyperlink ref="H83" r:id="rId49" xr:uid="{730ADE1D-7AB1-4045-9605-7178FD603068}"/>
-    <hyperlink ref="H89" r:id="rId50" xr:uid="{8C1B7032-C130-4830-8768-7433E109FA02}"/>
-    <hyperlink ref="H78" r:id="rId51" xr:uid="{FC41B6AC-5E57-43F7-9402-1C9117121189}"/>
-    <hyperlink ref="H81" r:id="rId52" xr:uid="{9E952813-F017-47F5-9544-C1D5E758C359}"/>
-    <hyperlink ref="H84" r:id="rId53" xr:uid="{AD155B72-4E79-4429-A06A-2C4B16FFF33D}"/>
-    <hyperlink ref="H87" r:id="rId54" xr:uid="{F6456D77-05F5-4173-B6CA-70260CBB0A58}"/>
-    <hyperlink ref="H90" r:id="rId55" xr:uid="{48433DED-C1F8-4D6C-B214-3A279505B2D6}"/>
-    <hyperlink ref="H76" r:id="rId56" xr:uid="{6B52B382-D1D4-4DFB-B626-874F8F7EDF18}"/>
-    <hyperlink ref="H79" r:id="rId57" xr:uid="{D24AAA7A-A72E-4097-BD9D-A877399EE09E}"/>
-    <hyperlink ref="H82" r:id="rId58" xr:uid="{B5167D5B-4C9D-46DE-A07F-27373B9B2DE4}"/>
-    <hyperlink ref="H85" r:id="rId59" xr:uid="{0C5F9D97-8070-4C07-8BB3-8B4B505E347B}"/>
-    <hyperlink ref="H88" r:id="rId60" xr:uid="{9EBA3E94-3443-46E5-8FAE-260C4505C2E0}"/>
-    <hyperlink ref="H91" r:id="rId61" xr:uid="{14F7D100-BBD2-468A-8F3F-D75D96FC7685}"/>
-    <hyperlink ref="H71" r:id="rId62" xr:uid="{2083F290-F1F6-478A-8B25-82B485B2F3C9}"/>
-    <hyperlink ref="H65" r:id="rId63" xr:uid="{D94A52F2-BAB9-460F-BBEA-98F02A7FDA35}"/>
+    <hyperlink ref="H60" r:id="rId30" xr:uid="{5AE8628B-A6AC-4465-BD4E-F82D7A992971}"/>
+    <hyperlink ref="H63" r:id="rId31" xr:uid="{5CF7566F-CBE0-4F25-9013-93E6C3867D34}"/>
+    <hyperlink ref="H88" r:id="rId32" xr:uid="{1C353C88-9EE8-4F55-ABF4-3CDB7B4E6AFA}"/>
+    <hyperlink ref="H70" r:id="rId33" xr:uid="{A4884050-FCBA-4619-993B-8E09E8C3C70B}"/>
+    <hyperlink ref="H72" r:id="rId34" xr:uid="{58D76656-D3D8-42D0-BC20-8510076538AB}"/>
+    <hyperlink ref="H75" r:id="rId35" xr:uid="{C0E7B505-5AEC-4726-BC3C-849B7BDA23D9}"/>
+    <hyperlink ref="H61" r:id="rId36" xr:uid="{8C7DE950-390F-4072-944E-544CAC30E1E2}"/>
+    <hyperlink ref="H64" r:id="rId37" xr:uid="{B704CBA7-EC39-4C16-9B7C-5A1F23168BB8}"/>
+    <hyperlink ref="H68" r:id="rId38" xr:uid="{77992806-B822-4851-8E7E-B16BCD52945D}"/>
+    <hyperlink ref="H71" r:id="rId39" xr:uid="{70DB7A6C-EE09-443B-AD3C-19A4D772B8A8}"/>
+    <hyperlink ref="H66" r:id="rId40" xr:uid="{D424DDC5-5012-4B92-A954-F4FB9A628B30}"/>
+    <hyperlink ref="H76" r:id="rId41" xr:uid="{0B10C842-555F-4DE2-9434-D8A68A89D8EB}"/>
+    <hyperlink ref="H62" r:id="rId42" xr:uid="{C77D7737-0D5E-4663-A3E3-874018F1FFE3}"/>
+    <hyperlink ref="H65" r:id="rId43" xr:uid="{F1705702-B968-4193-861D-2AB08339CEE2}"/>
+    <hyperlink ref="H69" r:id="rId44" xr:uid="{D1806A47-31AD-4D52-9D39-FCC2CFADBCA7}"/>
+    <hyperlink ref="H74" r:id="rId45" xr:uid="{6D5ED102-4BF2-4DF0-9937-E6866027A220}"/>
+    <hyperlink ref="H77" r:id="rId46" xr:uid="{772C27DA-BD2C-4F9A-A4D3-5C6979B2A4F9}"/>
+    <hyperlink ref="H79" r:id="rId47" xr:uid="{EE876AD6-690E-4842-9C9C-46D511C113AC}"/>
+    <hyperlink ref="H82" r:id="rId48" xr:uid="{EDBE8CFB-1752-473F-8585-E99FE96B416C}"/>
+    <hyperlink ref="H85" r:id="rId49" xr:uid="{730ADE1D-7AB1-4045-9605-7178FD603068}"/>
+    <hyperlink ref="H91" r:id="rId50" xr:uid="{8C1B7032-C130-4830-8768-7433E109FA02}"/>
+    <hyperlink ref="H80" r:id="rId51" xr:uid="{FC41B6AC-5E57-43F7-9402-1C9117121189}"/>
+    <hyperlink ref="H83" r:id="rId52" xr:uid="{9E952813-F017-47F5-9544-C1D5E758C359}"/>
+    <hyperlink ref="H86" r:id="rId53" xr:uid="{AD155B72-4E79-4429-A06A-2C4B16FFF33D}"/>
+    <hyperlink ref="H89" r:id="rId54" xr:uid="{F6456D77-05F5-4173-B6CA-70260CBB0A58}"/>
+    <hyperlink ref="H92" r:id="rId55" xr:uid="{48433DED-C1F8-4D6C-B214-3A279505B2D6}"/>
+    <hyperlink ref="H78" r:id="rId56" xr:uid="{6B52B382-D1D4-4DFB-B626-874F8F7EDF18}"/>
+    <hyperlink ref="H81" r:id="rId57" xr:uid="{D24AAA7A-A72E-4097-BD9D-A877399EE09E}"/>
+    <hyperlink ref="H84" r:id="rId58" xr:uid="{B5167D5B-4C9D-46DE-A07F-27373B9B2DE4}"/>
+    <hyperlink ref="H87" r:id="rId59" xr:uid="{0C5F9D97-8070-4C07-8BB3-8B4B505E347B}"/>
+    <hyperlink ref="H90" r:id="rId60" xr:uid="{9EBA3E94-3443-46E5-8FAE-260C4505C2E0}"/>
+    <hyperlink ref="H93" r:id="rId61" xr:uid="{14F7D100-BBD2-468A-8F3F-D75D96FC7685}"/>
+    <hyperlink ref="H73" r:id="rId62" xr:uid="{2083F290-F1F6-478A-8B25-82B485B2F3C9}"/>
+    <hyperlink ref="H67" r:id="rId63" xr:uid="{D94A52F2-BAB9-460F-BBEA-98F02A7FDA35}"/>
     <hyperlink ref="H18" r:id="rId64" xr:uid="{356A992B-7C92-430E-BC27-C451BB111F05}"/>
     <hyperlink ref="H10" r:id="rId65" xr:uid="{B1663DD2-D1A3-494E-BB22-F085B519E4E7}"/>
     <hyperlink ref="H13" r:id="rId66" xr:uid="{EECAB09E-B6D1-4B40-A043-FB12E69D4217}"/>
@@ -5471,25 +5537,25 @@
     <hyperlink ref="H29" r:id="rId71" xr:uid="{B00D18A3-39BF-4A4C-BE3B-C1D2830C1E48}"/>
     <hyperlink ref="H33" r:id="rId72" xr:uid="{74FE14DD-CBA5-4C95-BC88-BBF2012B3C5F}"/>
     <hyperlink ref="H25" r:id="rId73" xr:uid="{9B0B094A-37C5-4822-90D8-9D93F902484F}"/>
-    <hyperlink ref="H55" r:id="rId74" xr:uid="{35903F7D-00A7-43CD-8F44-E9000683A9A3}"/>
+    <hyperlink ref="H57" r:id="rId74" xr:uid="{35903F7D-00A7-43CD-8F44-E9000683A9A3}"/>
     <hyperlink ref="H34" r:id="rId75" xr:uid="{67189A5A-22B6-42C9-AA91-8FA46DC05B1B}"/>
     <hyperlink ref="H40" r:id="rId76" xr:uid="{F02C8D74-71A0-4E52-A4CC-A4C959B933D0}"/>
-    <hyperlink ref="H94" r:id="rId77" xr:uid="{7ABFE093-A499-460B-8A3A-747B903CC0D8}"/>
-    <hyperlink ref="H97" r:id="rId78" xr:uid="{2B763DFA-8E55-4423-94F6-F97B6347E7BA}"/>
-    <hyperlink ref="H92" r:id="rId79" xr:uid="{6780C0A0-5A66-4E8D-AF30-69EA7BFFD49D}"/>
-    <hyperlink ref="H95" r:id="rId80" xr:uid="{DB91D74C-E4FC-436A-AEF8-93FBD178CBBE}"/>
-    <hyperlink ref="H98" r:id="rId81" xr:uid="{B7219162-37EA-4A3E-B4C7-3F521EBFD599}"/>
-    <hyperlink ref="H93" r:id="rId82" xr:uid="{CE50F847-61E3-4A9F-8A44-97EECA535CE9}"/>
-    <hyperlink ref="H96" r:id="rId83" xr:uid="{D03A9A92-D0F9-4AFC-9B83-5CC2D1783E1B}"/>
-    <hyperlink ref="H99" r:id="rId84" xr:uid="{A8395A87-E3FD-4CE6-AFB3-200935279EA6}"/>
-    <hyperlink ref="H102" r:id="rId85" xr:uid="{013730CB-39A8-4695-9BF8-C407D6F34505}"/>
-    <hyperlink ref="H100" r:id="rId86" xr:uid="{27CF8E39-5B7F-4666-918E-5055CEFD74BC}"/>
-    <hyperlink ref="H103" r:id="rId87" xr:uid="{EDB2E061-0439-4233-8D8F-01AA45D54C99}"/>
-    <hyperlink ref="H101" r:id="rId88" xr:uid="{02CBD326-C1AD-4AAC-97A3-A39AC2978547}"/>
-    <hyperlink ref="H104" r:id="rId89" xr:uid="{6F247405-8D2E-4DC1-939B-8BF6AACD2BF1}"/>
-    <hyperlink ref="H107" r:id="rId90" xr:uid="{D0E30AF2-28B4-409A-8AAB-442272946FD0}"/>
-    <hyperlink ref="H105" r:id="rId91" xr:uid="{32D50C06-9C81-414D-B5C1-43F98F5AAEBC}"/>
-    <hyperlink ref="H106" r:id="rId92" xr:uid="{9B663D42-A486-4D62-8F2A-96A28A5757C7}"/>
+    <hyperlink ref="H96" r:id="rId77" xr:uid="{7ABFE093-A499-460B-8A3A-747B903CC0D8}"/>
+    <hyperlink ref="H99" r:id="rId78" xr:uid="{2B763DFA-8E55-4423-94F6-F97B6347E7BA}"/>
+    <hyperlink ref="H94" r:id="rId79" xr:uid="{6780C0A0-5A66-4E8D-AF30-69EA7BFFD49D}"/>
+    <hyperlink ref="H97" r:id="rId80" xr:uid="{DB91D74C-E4FC-436A-AEF8-93FBD178CBBE}"/>
+    <hyperlink ref="H100" r:id="rId81" xr:uid="{B7219162-37EA-4A3E-B4C7-3F521EBFD599}"/>
+    <hyperlink ref="H95" r:id="rId82" xr:uid="{CE50F847-61E3-4A9F-8A44-97EECA535CE9}"/>
+    <hyperlink ref="H98" r:id="rId83" xr:uid="{D03A9A92-D0F9-4AFC-9B83-5CC2D1783E1B}"/>
+    <hyperlink ref="H101" r:id="rId84" xr:uid="{A8395A87-E3FD-4CE6-AFB3-200935279EA6}"/>
+    <hyperlink ref="H104" r:id="rId85" xr:uid="{013730CB-39A8-4695-9BF8-C407D6F34505}"/>
+    <hyperlink ref="H102" r:id="rId86" xr:uid="{27CF8E39-5B7F-4666-918E-5055CEFD74BC}"/>
+    <hyperlink ref="H105" r:id="rId87" xr:uid="{EDB2E061-0439-4233-8D8F-01AA45D54C99}"/>
+    <hyperlink ref="H103" r:id="rId88" xr:uid="{02CBD326-C1AD-4AAC-97A3-A39AC2978547}"/>
+    <hyperlink ref="H106" r:id="rId89" xr:uid="{6F247405-8D2E-4DC1-939B-8BF6AACD2BF1}"/>
+    <hyperlink ref="H109" r:id="rId90" xr:uid="{D0E30AF2-28B4-409A-8AAB-442272946FD0}"/>
+    <hyperlink ref="H107" r:id="rId91" xr:uid="{32D50C06-9C81-414D-B5C1-43F98F5AAEBC}"/>
+    <hyperlink ref="H108" r:id="rId92" xr:uid="{9B663D42-A486-4D62-8F2A-96A28A5757C7}"/>
     <hyperlink ref="H6" r:id="rId93" xr:uid="{A4F101D3-BF5A-4795-A827-98C9ACD6D091}"/>
     <hyperlink ref="H22" r:id="rId94" xr:uid="{79FB6451-2479-47C4-A438-3105DA92B082}"/>
     <hyperlink ref="H44" r:id="rId95" xr:uid="{3CD53464-4392-44A1-A246-A2BC21D8DAD5}"/>
@@ -5503,9 +5569,11 @@
     <hyperlink ref="H30" r:id="rId103" xr:uid="{C7B34DA6-516D-4E52-9058-B4ECE30B70DD}"/>
     <hyperlink ref="H31" r:id="rId104" xr:uid="{87540BE4-3D29-45F0-B9E0-052DDCCA467D}"/>
     <hyperlink ref="H32" r:id="rId105" xr:uid="{1CED9159-C2D3-4B5C-AFCA-EC78DF96FC5E}"/>
+    <hyperlink ref="H55" r:id="rId106" xr:uid="{E4C7294A-7DAC-438C-A0C1-3C166E1D7B30}"/>
+    <hyperlink ref="H56" r:id="rId107" xr:uid="{60149C6E-5E16-4F2C-9B43-02383B4B67A6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId106"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId108"/>
 </worksheet>
 </file>
 
@@ -10091,8 +10159,8 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12"/>
       <c r="D5">
-        <f>SUM(Europe!I3:I107)+SUM(America!I3:I25)+SUM(Africa!I3:I12)+SUM('Australia and Oceania'!I3:I21)+SUM(Asia!I3:I70)-100</f>
-        <v>132.76000000000005</v>
+        <f>SUM(Europe!I3:I109)+SUM(America!I3:I25)+SUM(Africa!I3:I12)+SUM('Australia and Oceania'!I3:I21)+SUM(Asia!I3:I70)-100</f>
+        <v>133.38000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
